--- a/docs/mmm.xlsx
+++ b/docs/mmm.xlsx
@@ -26,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="&amp;quot;¥&amp;quot;#,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color rgb="1"/>
@@ -78,37 +78,32 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00FF00"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF2278"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="3">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
+  <fills count="5">
+    <fill>
+      <patternFill patternType="none">
+        <fgColor rgb="FFFFFF33"/>
+        <bgColor rgb="646464"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <bgColor rgb="646464"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0000FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF2278"/>
       </patternFill>
     </fill>
   </fills>
@@ -124,9 +119,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -134,10 +132,10 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="1" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -331,20 +329,20 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>2</v>
       </c>
     </row>
